--- a/Excel/EquipSuitPropertyConfig.xlsx
+++ b/Excel/EquipSuitPropertyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91AF3360-385C-4BD7-B158-81114EEBD857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9721A05-5F78-4F31-9B21-50F4FB5E91A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitPropertyProto" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="320">
   <si>
     <t>Id</t>
   </si>
@@ -853,235 +853,232 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>Attack increases by 20</t>
-  </si>
-  <si>
-    <t>Crit rate increases by 3%</t>
-  </si>
-  <si>
-    <t>Attack increases by 30</t>
-  </si>
-  <si>
-    <t>Magic defense increased by 30</t>
-  </si>
-  <si>
-    <t>Attack power increased by 50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hit rate increases by 3% </t>
-  </si>
-  <si>
-    <t>Defense increases by 20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Damage reduction increased by 3% </t>
-  </si>
-  <si>
-    <t>Health increased by 200 points</t>
-  </si>
-  <si>
-    <t>Damage bonus increased by 3%</t>
-  </si>
-  <si>
-    <t>Dodge rate increased by 3%</t>
-  </si>
-  <si>
-    <t>Hit rate increase by 4%</t>
-  </si>
-  <si>
-    <t>Attack power is increased by 75.</t>
-  </si>
-  <si>
-    <t>Critical hit rate increased by 5%</t>
-  </si>
-  <si>
-    <t>Defense increased by 30, Magic Defense increased by 30</t>
-  </si>
-  <si>
-    <t>Damage bonus increased by 4%</t>
-  </si>
-  <si>
-    <t>Movement speed increased by 5%</t>
-  </si>
-  <si>
-    <t>Blood quantity increased by 320 points</t>
-  </si>
-  <si>
-    <t>Increased critical hit rate by 5%</t>
-  </si>
-  <si>
-    <t>Attack increases by 100 points</t>
-  </si>
-  <si>
-    <t>Skill damage increased by 100 points</t>
-  </si>
-  <si>
-    <t>Damage increase by 5%</t>
-  </si>
-  <si>
-    <t>Hit rate increased by 5%</t>
-  </si>
-  <si>
-    <t>Attack increased by 125 points</t>
-  </si>
-  <si>
-    <t>Defense increases by 50 and Magic Defense increases by 50.</t>
-  </si>
-  <si>
-    <t>Damage reduction increased by 5%</t>
-  </si>
-  <si>
-    <t>Evasion rate +5%.</t>
-  </si>
-  <si>
-    <t>Defense increased by 75 Magic defense increased by 75</t>
-  </si>
-  <si>
-    <t>Attack power increases by 150.</t>
-  </si>
-  <si>
-    <t>Attack and magic penetration increase by 5%</t>
-  </si>
-  <si>
-    <t>Attack increased by 120</t>
-  </si>
-  <si>
-    <t>Physical defense increased by 150 points</t>
-  </si>
-  <si>
-    <t>Increases attack speed by 5%</t>
-  </si>
-  <si>
-    <t>Health increased by 600 points</t>
-  </si>
-  <si>
-    <t>Damage received reflects 5% of the damage as reflected damage to the target</t>
-  </si>
-  <si>
-    <t>Attack power increased by 200</t>
-  </si>
-  <si>
-    <t>Health increases by 750 points.</t>
-  </si>
-  <si>
-    <t>Increased evasion probability by 5%</t>
-  </si>
-  <si>
-    <t>True damage increased by 200 points</t>
-  </si>
-  <si>
-    <t>Skill cooldown time reduced by 5%</t>
-  </si>
-  <si>
-    <t>Attack power increased by 5%</t>
-  </si>
-  <si>
-    <t>Ignore the target's defense value of 300 points</t>
-  </si>
-  <si>
-    <t>Increase the maximum life by 5%</t>
-  </si>
-  <si>
-    <t>True Damage Increases by 300 points</t>
-  </si>
-  <si>
-    <t>Ignore target defense value by 400 points</t>
-  </si>
-  <si>
-    <t>Magic Defense +1%</t>
-  </si>
-  <si>
-    <t>Spell +1%</t>
-  </si>
-  <si>
-    <t>Critical Hit + 1%</t>
-  </si>
-  <si>
-    <t>Defense + 1%</t>
-  </si>
-  <si>
     <t>Attack +1%</t>
   </si>
   <si>
-    <t>Hit Rate +1%</t>
-  </si>
-  <si>
-    <t>Anti-riot + 1%</t>
-  </si>
-  <si>
-    <t>Health + 1%</t>
-  </si>
-  <si>
-    <t>Dodge +1%</t>
-  </si>
-  <si>
-    <t>Magic defense + 1.5%</t>
-  </si>
-  <si>
-    <t>Spell +1.5%</t>
-  </si>
-  <si>
-    <t>Critical hit + 1.5%</t>
-  </si>
-  <si>
-    <t>Defense +1.5%</t>
-  </si>
-  <si>
-    <t>Attack + 1.5%</t>
-  </si>
-  <si>
-    <t>Hit rate +1.5%</t>
-  </si>
-  <si>
-    <t>Increased resistance to damage by 1.5%</t>
-  </si>
-  <si>
-    <t>Health + 1.5%</t>
-  </si>
-  <si>
-    <t>Dodge +1.5%</t>
-  </si>
-  <si>
-    <t>Magic Defense + 2%</t>
-  </si>
-  <si>
-    <t>Spell Power + 2%</t>
-  </si>
-  <si>
-    <t>Critical Hit +2%</t>
-  </si>
-  <si>
-    <t>Physical Defense + 2%</t>
-  </si>
-  <si>
-    <t>Attack + 2%</t>
-  </si>
-  <si>
-    <t>Hit rate +2%</t>
-  </si>
-  <si>
-    <t>Anti-riot + 2%</t>
-  </si>
-  <si>
-    <t>Health + 2%</t>
-  </si>
-  <si>
-    <t>Dodge increased by 2%</t>
-  </si>
-  <si>
-    <t>Strength + 20</t>
-  </si>
-  <si>
     <t>Agility +20</t>
   </si>
   <si>
     <t>Stamina +20</t>
   </si>
   <si>
-    <t>+20 to Stamina</t>
-  </si>
-  <si>
-    <t>Intelligence + 20</t>
+    <t>Attack +20</t>
+  </si>
+  <si>
+    <t>Crit Rate +3%</t>
+  </si>
+  <si>
+    <t>Attack +30</t>
+  </si>
+  <si>
+    <t>Magic Def +30</t>
+  </si>
+  <si>
+    <t>Hit Rate +3%</t>
+  </si>
+  <si>
+    <t>Defense +20</t>
+  </si>
+  <si>
+    <t>Dmg Reduction +3%</t>
+  </si>
+  <si>
+    <t>HP +200</t>
+  </si>
+  <si>
+    <t>Dmg Bonus +3%</t>
+  </si>
+  <si>
+    <t>Evasion Rate +3%</t>
+  </si>
+  <si>
+    <t>Hit Rate +4%</t>
+  </si>
+  <si>
+    <t>Attack +75</t>
+  </si>
+  <si>
+    <t>Def/Magic Def +30</t>
+  </si>
+  <si>
+    <t>Dmg Bonus +4%</t>
+  </si>
+  <si>
+    <t>Move Speed +5%</t>
+  </si>
+  <si>
+    <t>HP +320</t>
+  </si>
+  <si>
+    <t>Smash Rate +5%</t>
+  </si>
+  <si>
+    <t>Attack +100</t>
+  </si>
+  <si>
+    <t>Skill Dmg +100</t>
+  </si>
+  <si>
+    <t>Attack +125</t>
+  </si>
+  <si>
+    <t>Def/Magic Def +50</t>
+  </si>
+  <si>
+    <t>Dmg Reduction +5%</t>
+  </si>
+  <si>
+    <t>Evasion Rate +5%</t>
+  </si>
+  <si>
+    <t>Def/Magic Def +75</t>
+  </si>
+  <si>
+    <t>Attack +150</t>
+  </si>
+  <si>
+    <t>Atk/Magic Pen +5%</t>
+  </si>
+  <si>
+    <t>Physical Def +150</t>
+  </si>
+  <si>
+    <t>Attack Speed +5%</t>
+  </si>
+  <si>
+    <t>HP +600</t>
+  </si>
+  <si>
+    <t>5% Dmg Reflect on Hit</t>
+  </si>
+  <si>
+    <t>Attack +200</t>
+  </si>
+  <si>
+    <t>HP +750</t>
+  </si>
+  <si>
+    <t>True Dmg +200</t>
+  </si>
+  <si>
+    <t>Cooldown -5%</t>
+  </si>
+  <si>
+    <t>Attack +5%</t>
+  </si>
+  <si>
+    <t>Ignore Def +300</t>
+  </si>
+  <si>
+    <t>Max HP +5%</t>
+  </si>
+  <si>
+    <t>True Dmg +300</t>
+  </si>
+  <si>
+    <t>Ignore Def +400</t>
+  </si>
+  <si>
+    <t>Magic Def +1%</t>
+  </si>
+  <si>
+    <t>Spell Power +1%</t>
+  </si>
+  <si>
+    <t>Crit +1%</t>
+  </si>
+  <si>
+    <t>Physical Def +1%</t>
+  </si>
+  <si>
+    <t>Hit +1%</t>
+  </si>
+  <si>
+    <t>Crit Resistance +1%</t>
+  </si>
+  <si>
+    <t>HP +1%</t>
+  </si>
+  <si>
+    <t>Evasion +1%</t>
+  </si>
+  <si>
+    <t>Strength +20</t>
+  </si>
+  <si>
+    <t>Vitality +20</t>
+  </si>
+  <si>
+    <t>Intelligence +20</t>
+  </si>
+  <si>
+    <t>Attack +50</t>
+  </si>
+  <si>
+    <t>Crit Rate +5%</t>
+  </si>
+  <si>
+    <t>Dmg Bonus +5%</t>
+  </si>
+  <si>
+    <t>Hit Rate +5%</t>
+  </si>
+  <si>
+    <t>Attack +120</t>
+  </si>
+  <si>
+    <t>Magic Def +1.5%</t>
+  </si>
+  <si>
+    <t>Spell Power +1.5%</t>
+  </si>
+  <si>
+    <t>Crit +1.5%</t>
+  </si>
+  <si>
+    <t>Physical Def +1.5%</t>
+  </si>
+  <si>
+    <t>Attack +1.5%</t>
+  </si>
+  <si>
+    <t>Hit +1.5%</t>
+  </si>
+  <si>
+    <t>Crit Resistance +1.5%</t>
+  </si>
+  <si>
+    <t>HP +1.5%</t>
+  </si>
+  <si>
+    <t>Evasion +1.5%</t>
+  </si>
+  <si>
+    <t>Magic Def +2%</t>
+  </si>
+  <si>
+    <t>Spell Power +2%</t>
+  </si>
+  <si>
+    <t>Crit +2%</t>
+  </si>
+  <si>
+    <t>Physical Def +2%</t>
+  </si>
+  <si>
+    <t>Attack +2%</t>
+  </si>
+  <si>
+    <t>Hit +2%</t>
+  </si>
+  <si>
+    <t>Crit Resistance +2%</t>
+  </si>
+  <si>
+    <t>HP +2%</t>
+  </si>
+  <si>
+    <t>Evasion +2%</t>
   </si>
 </sst>
 </file>
@@ -7209,7 +7206,7 @@
         <v>125</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G56" s="14">
         <v>0</v>
@@ -7280,7 +7277,7 @@
         <v>126</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G57" s="14">
         <v>0</v>
@@ -7351,7 +7348,7 @@
         <v>127</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G58" s="14">
         <v>0</v>
@@ -7422,7 +7419,7 @@
         <v>125</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="G59" s="14">
         <v>0</v>
@@ -7493,7 +7490,7 @@
         <v>126</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G60" s="14">
         <v>0</v>
@@ -7564,7 +7561,7 @@
         <v>127</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G61" s="14">
         <v>0</v>
@@ -7635,7 +7632,7 @@
         <v>127</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G62" s="14">
         <v>0</v>
@@ -7706,7 +7703,7 @@
         <v>126</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="G63" s="14">
         <v>0</v>
@@ -7777,7 +7774,7 @@
         <v>127</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="G64" s="14">
         <v>0</v>
@@ -7848,7 +7845,7 @@
         <v>131</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="G65" s="19">
         <v>0</v>
@@ -7919,7 +7916,7 @@
         <v>132</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="G66" s="19">
         <v>0</v>
@@ -7990,7 +7987,7 @@
         <v>133</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="G67" s="19">
         <v>0</v>
@@ -8061,7 +8058,7 @@
         <v>134</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="G68" s="19">
         <v>0</v>
@@ -8132,7 +8129,7 @@
         <v>132</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>248</v>
+        <v>297</v>
       </c>
       <c r="G69" s="19">
         <v>0</v>
@@ -8203,7 +8200,7 @@
         <v>135</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="G70" s="19">
         <v>0</v>
@@ -8274,7 +8271,7 @@
         <v>136</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G71" s="19">
         <v>0</v>
@@ -8345,7 +8342,7 @@
         <v>137</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="G72" s="19">
         <v>0</v>
@@ -8416,7 +8413,7 @@
         <v>138</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G73" s="19">
         <v>0</v>
@@ -8487,7 +8484,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G74" s="19">
         <v>0</v>
@@ -8558,7 +8555,7 @@
         <v>139</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="G75" s="19">
         <v>0</v>
@@ -8629,7 +8626,7 @@
         <v>140</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G76" s="19">
         <v>0</v>
@@ -8700,7 +8697,7 @@
         <v>141</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G77" s="19">
         <v>0</v>
@@ -8771,7 +8768,7 @@
         <v>142</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G78" s="19">
         <v>0</v>
@@ -8842,7 +8839,7 @@
         <v>143</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G79" s="19">
         <v>0</v>
@@ -8913,7 +8910,7 @@
         <v>145</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G80" s="19">
         <v>0</v>
@@ -8984,7 +8981,7 @@
         <v>146</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G81" s="19">
         <v>0</v>
@@ -9055,7 +9052,7 @@
         <v>148</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G82" s="19">
         <v>0</v>
@@ -9126,7 +9123,7 @@
         <v>149</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G83" s="19">
         <v>0</v>
@@ -9197,7 +9194,7 @@
         <v>143</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="G84" s="19">
         <v>0</v>
@@ -9268,7 +9265,7 @@
         <v>150</v>
       </c>
       <c r="F85" s="23" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G85" s="19">
         <v>0</v>
@@ -9339,7 +9336,7 @@
         <v>151</v>
       </c>
       <c r="F86" s="23" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="G86" s="19">
         <v>0</v>
@@ -9410,7 +9407,7 @@
         <v>152</v>
       </c>
       <c r="F87" s="23" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G87" s="19">
         <v>0</v>
@@ -9481,7 +9478,7 @@
         <v>140</v>
       </c>
       <c r="F88" s="23" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G88" s="19">
         <v>0</v>
@@ -9552,7 +9549,7 @@
         <v>153</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G89" s="19">
         <v>0</v>
@@ -9623,7 +9620,7 @@
         <v>154</v>
       </c>
       <c r="F90" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G90" s="19">
         <v>0</v>
@@ -9694,7 +9691,7 @@
         <v>155</v>
       </c>
       <c r="F91" s="23" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G91" s="19">
         <v>0</v>
@@ -9765,7 +9762,7 @@
         <v>156</v>
       </c>
       <c r="F92" s="23" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G92" s="19">
         <v>0</v>
@@ -9836,7 +9833,7 @@
         <v>157</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G93" s="19">
         <v>0</v>
@@ -9907,7 +9904,7 @@
         <v>158</v>
       </c>
       <c r="F94" s="23" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G94" s="19">
         <v>0</v>
@@ -9978,7 +9975,7 @@
         <v>160</v>
       </c>
       <c r="F95" s="23" t="s">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="G95" s="19">
         <v>0</v>
@@ -10049,7 +10046,7 @@
         <v>161</v>
       </c>
       <c r="F96" s="22" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G96" s="14">
         <v>0</v>
@@ -10120,7 +10117,7 @@
         <v>162</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G97" s="19">
         <v>0</v>
@@ -10191,7 +10188,7 @@
         <v>164</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G98" s="19">
         <v>0</v>
@@ -10262,7 +10259,7 @@
         <v>154</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G99" s="19">
         <v>0</v>
@@ -10333,7 +10330,7 @@
         <v>165</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G100" s="19">
         <v>0</v>
@@ -10404,7 +10401,7 @@
         <v>157</v>
       </c>
       <c r="F101" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G101" s="14">
         <v>0</v>
@@ -10475,7 +10472,7 @@
         <v>151</v>
       </c>
       <c r="F102" s="22" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="G102" s="14">
         <v>0</v>
@@ -10546,7 +10543,7 @@
         <v>140</v>
       </c>
       <c r="F103" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G103" s="14">
         <v>0</v>
@@ -10617,7 +10614,7 @@
         <v>157</v>
       </c>
       <c r="F104" s="22" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G104" s="14">
         <v>0</v>
@@ -10688,7 +10685,7 @@
         <v>167</v>
       </c>
       <c r="F105" s="22" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G105" s="14">
         <v>0</v>
@@ -10759,7 +10756,7 @@
         <v>150</v>
       </c>
       <c r="F106" s="22" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G106" s="14">
         <v>0</v>
@@ -10830,7 +10827,7 @@
         <v>168</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G107" s="14">
         <v>0</v>
@@ -10901,7 +10898,7 @@
         <v>169</v>
       </c>
       <c r="F108" s="22" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G108" s="14">
         <v>0</v>
@@ -10972,7 +10969,7 @@
         <v>146</v>
       </c>
       <c r="F109" s="22" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G109" s="14">
         <v>0</v>
@@ -11043,7 +11040,7 @@
         <v>171</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="G110" s="14">
         <v>0</v>
@@ -11114,7 +11111,7 @@
         <v>140</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G111" s="14">
         <v>0</v>
@@ -11185,7 +11182,7 @@
         <v>173</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G112" s="14">
         <v>0</v>
@@ -11256,7 +11253,7 @@
         <v>175</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G113" s="14">
         <v>0</v>
@@ -11327,7 +11324,7 @@
         <v>140</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G114" s="14">
         <v>0</v>
@@ -11398,7 +11395,7 @@
         <v>150</v>
       </c>
       <c r="F115" s="22" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G115" s="14">
         <v>0</v>
@@ -11469,7 +11466,7 @@
         <v>177</v>
       </c>
       <c r="F116" s="22" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G116" s="14">
         <v>0</v>
@@ -11540,7 +11537,7 @@
         <v>169</v>
       </c>
       <c r="F117" s="22" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G117" s="14">
         <v>0</v>
@@ -11611,7 +11608,7 @@
         <v>179</v>
       </c>
       <c r="F118" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G118" s="14">
         <v>0</v>
@@ -11682,7 +11679,7 @@
         <v>225</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G119" s="14">
         <v>0</v>
@@ -11753,7 +11750,7 @@
         <v>140</v>
       </c>
       <c r="F120" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G120" s="14">
         <v>0</v>
@@ -11824,7 +11821,7 @@
         <v>173</v>
       </c>
       <c r="F121" s="22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G121" s="14">
         <v>0</v>
@@ -11895,7 +11892,7 @@
         <v>175</v>
       </c>
       <c r="F122" s="22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G122" s="14">
         <v>0</v>
@@ -11966,7 +11963,7 @@
         <v>140</v>
       </c>
       <c r="F123" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G123" s="14">
         <v>0</v>
@@ -12037,7 +12034,7 @@
         <v>150</v>
       </c>
       <c r="F124" s="22" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G124" s="14">
         <v>0</v>
@@ -12108,7 +12105,7 @@
         <v>226</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G125" s="14">
         <v>0</v>
@@ -12179,7 +12176,7 @@
         <v>169</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G126" s="14">
         <v>0</v>
@@ -12250,7 +12247,7 @@
         <v>179</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G127" s="14">
         <v>0</v>
@@ -12321,7 +12318,7 @@
         <v>225</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="G128" s="14">
         <v>0</v>
@@ -12392,7 +12389,7 @@
         <v>140</v>
       </c>
       <c r="F129" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G129" s="14">
         <v>0</v>
@@ -12463,7 +12460,7 @@
         <v>173</v>
       </c>
       <c r="F130" s="22" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="G130" s="14">
         <v>0</v>
@@ -12534,7 +12531,7 @@
         <v>175</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="G131" s="14">
         <v>0</v>
@@ -12605,7 +12602,7 @@
         <v>140</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G132" s="14">
         <v>0</v>
@@ -12676,7 +12673,7 @@
         <v>150</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>265</v>
+        <v>299</v>
       </c>
       <c r="G133" s="14">
         <v>0</v>
@@ -12747,7 +12744,7 @@
         <v>226</v>
       </c>
       <c r="F134" s="22" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G134" s="14">
         <v>0</v>
@@ -12818,7 +12815,7 @@
         <v>169</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="G135" s="14">
         <v>0</v>
@@ -12889,7 +12886,7 @@
         <v>179</v>
       </c>
       <c r="F136" s="22" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="G136" s="14">
         <v>0</v>
@@ -12960,7 +12957,7 @@
         <v>140</v>
       </c>
       <c r="F137" s="22" t="s">
-        <v>257</v>
+        <v>298</v>
       </c>
       <c r="G137" s="14">
         <v>0</v>
@@ -13031,7 +13028,7 @@
         <v>184</v>
       </c>
       <c r="F138" s="22" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="G138" s="14">
         <v>0</v>
@@ -13102,7 +13099,7 @@
         <v>185</v>
       </c>
       <c r="F139" s="22" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="G139" s="14">
         <v>0</v>
@@ -13173,7 +13170,7 @@
         <v>183</v>
       </c>
       <c r="F140" s="22" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="G140" s="14">
         <v>0</v>
@@ -13244,7 +13241,7 @@
         <v>187</v>
       </c>
       <c r="F141" s="22" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G141" s="14">
         <v>0</v>
@@ -13315,7 +13312,7 @@
         <v>188</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>293</v>
+        <v>244</v>
       </c>
       <c r="G142" s="14">
         <v>0</v>
@@ -13386,7 +13383,7 @@
         <v>186</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="G143" s="14">
         <v>0</v>
@@ -13457,7 +13454,7 @@
         <v>190</v>
       </c>
       <c r="F144" s="22" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="G144" s="14">
         <v>0</v>
@@ -13528,7 +13525,7 @@
         <v>191</v>
       </c>
       <c r="F145" s="22" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="G145" s="14">
         <v>0</v>
@@ -13599,7 +13596,7 @@
         <v>189</v>
       </c>
       <c r="F146" s="22" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="G146" s="14">
         <v>0</v>
@@ -13670,7 +13667,7 @@
         <v>202</v>
       </c>
       <c r="F147" s="22" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G147" s="14">
         <v>0</v>
@@ -13741,7 +13738,7 @@
         <v>203</v>
       </c>
       <c r="F148" s="22" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G148" s="14">
         <v>0</v>
@@ -13812,7 +13809,7 @@
         <v>204</v>
       </c>
       <c r="F149" s="22" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="G149" s="14">
         <v>0</v>
@@ -13883,7 +13880,7 @@
         <v>205</v>
       </c>
       <c r="F150" s="22" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G150" s="14">
         <v>0</v>
@@ -13954,7 +13951,7 @@
         <v>206</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="G151" s="14">
         <v>0</v>
@@ -14025,7 +14022,7 @@
         <v>207</v>
       </c>
       <c r="F152" s="22" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G152" s="14">
         <v>0</v>
@@ -14096,7 +14093,7 @@
         <v>208</v>
       </c>
       <c r="F153" s="22" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="G153" s="14">
         <v>0</v>
@@ -14167,7 +14164,7 @@
         <v>209</v>
       </c>
       <c r="F154" s="22" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="G154" s="14">
         <v>0</v>
@@ -14238,7 +14235,7 @@
         <v>210</v>
       </c>
       <c r="F155" s="22" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="G155" s="14">
         <v>0</v>
@@ -14309,7 +14306,7 @@
         <v>211</v>
       </c>
       <c r="F156" s="22" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="G156" s="14">
         <v>0</v>
@@ -14380,7 +14377,7 @@
         <v>212</v>
       </c>
       <c r="F157" s="22" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="G157" s="14">
         <v>0</v>
@@ -14451,7 +14448,7 @@
         <v>213</v>
       </c>
       <c r="F158" s="22" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G158" s="14">
         <v>0</v>
@@ -14522,7 +14519,7 @@
         <v>214</v>
       </c>
       <c r="F159" s="22" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="G159" s="14">
         <v>0</v>
@@ -14593,7 +14590,7 @@
         <v>215</v>
       </c>
       <c r="F160" s="22" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="G160" s="14">
         <v>0</v>
@@ -14664,7 +14661,7 @@
         <v>216</v>
       </c>
       <c r="F161" s="22" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G161" s="14">
         <v>0</v>
@@ -14735,7 +14732,7 @@
         <v>217</v>
       </c>
       <c r="F162" s="22" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G162" s="14">
         <v>0</v>
@@ -14806,7 +14803,7 @@
         <v>218</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G163" s="14">
         <v>0</v>
@@ -14877,7 +14874,7 @@
         <v>219</v>
       </c>
       <c r="F164" s="22" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G164" s="14">
         <v>0</v>
@@ -14948,7 +14945,7 @@
         <v>229</v>
       </c>
       <c r="F165" s="22" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
       <c r="G165" s="14">
         <v>0</v>
@@ -15019,7 +15016,7 @@
         <v>230</v>
       </c>
       <c r="F166" s="22" t="s">
-        <v>317</v>
+        <v>245</v>
       </c>
       <c r="G166" s="14">
         <v>0</v>
@@ -15090,7 +15087,7 @@
         <v>219</v>
       </c>
       <c r="F167" s="22" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="G167" s="14">
         <v>0</v>
@@ -15161,7 +15158,7 @@
         <v>238</v>
       </c>
       <c r="F168" s="22" t="s">
-        <v>318</v>
+        <v>295</v>
       </c>
       <c r="G168" s="14">
         <v>0</v>
@@ -15232,7 +15229,7 @@
         <v>231</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>319</v>
+        <v>246</v>
       </c>
       <c r="G169" s="14">
         <v>0</v>
@@ -15303,7 +15300,7 @@
         <v>218</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G170" s="14">
         <v>0</v>
@@ -15374,7 +15371,7 @@
         <v>232</v>
       </c>
       <c r="F171" s="22" t="s">
-        <v>320</v>
+        <v>296</v>
       </c>
       <c r="G171" s="14">
         <v>0</v>
@@ -15445,7 +15442,7 @@
         <v>217</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G172" s="14">
         <v>0</v>
@@ -15516,7 +15513,7 @@
         <v>218</v>
       </c>
       <c r="F173" s="22" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="G173" s="14">
         <v>0</v>

--- a/Excel/EquipSuitPropertyConfig.xlsx
+++ b/Excel/EquipSuitPropertyConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9721A05-5F78-4F31-9B21-50F4FB5E91A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF82666-A4C0-48B0-A9C8-5F318156E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="326">
   <si>
     <t>Id</t>
   </si>
@@ -1079,6 +1079,30 @@
   </si>
   <si>
     <t>Evasion +2%</t>
+  </si>
+  <si>
+    <t>110301,400</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>True Dmg +400</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>真实伤害提高400点</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>118101,500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>忽视目标防御值500点</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ignore Def +500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1707,7 +1731,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:AI189"/>
+  <dimension ref="C1:AI198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="8.5" customWidth="1"/>
@@ -12801,7 +12825,7 @@
         <v>0</v>
       </c>
       <c r="Y134" s="20" t="s">
-        <v>227</v>
+        <v>323</v>
       </c>
     </row>
     <row r="135" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12947,122 +12971,122 @@
       </c>
     </row>
     <row r="137" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C137" s="12">
-        <v>200001</v>
+      <c r="C137" s="17">
+        <v>190111</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>181</v>
+        <v>130</v>
       </c>
       <c r="E137" s="13" t="s">
+        <v>322</v>
+      </c>
+      <c r="F137" s="22" t="s">
+        <v>321</v>
+      </c>
+      <c r="G137" s="14">
+        <v>0</v>
+      </c>
+      <c r="H137" s="12">
+        <v>0</v>
+      </c>
+      <c r="I137" s="12">
+        <v>0</v>
+      </c>
+      <c r="J137" s="12">
+        <v>0</v>
+      </c>
+      <c r="K137" s="12">
+        <v>0</v>
+      </c>
+      <c r="L137" s="12">
+        <v>0</v>
+      </c>
+      <c r="M137" s="14">
+        <v>0</v>
+      </c>
+      <c r="N137" s="14">
+        <v>0</v>
+      </c>
+      <c r="O137" s="14">
+        <v>0</v>
+      </c>
+      <c r="P137" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q137" s="12">
+        <v>0</v>
+      </c>
+      <c r="R137" s="12">
+        <v>0</v>
+      </c>
+      <c r="S137" s="12">
+        <v>0</v>
+      </c>
+      <c r="T137" s="12">
+        <v>0</v>
+      </c>
+      <c r="U137" s="12">
+        <v>0</v>
+      </c>
+      <c r="V137" s="12">
+        <v>0</v>
+      </c>
+      <c r="W137" s="12">
+        <v>0</v>
+      </c>
+      <c r="X137" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y137" s="20" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="138" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C138" s="17">
+        <v>190112</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="E138" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="F137" s="22" t="s">
+      <c r="F138" s="22" t="s">
         <v>298</v>
       </c>
-      <c r="G137" s="14">
-        <v>0</v>
-      </c>
-      <c r="H137" s="12">
-        <v>0</v>
-      </c>
-      <c r="I137" s="12">
-        <v>0</v>
-      </c>
-      <c r="J137" s="12">
-        <v>0</v>
-      </c>
-      <c r="K137" s="12">
-        <v>0</v>
-      </c>
-      <c r="L137" s="12">
-        <v>0</v>
-      </c>
-      <c r="M137" s="14">
-        <v>0</v>
-      </c>
-      <c r="N137" s="14">
-        <v>0</v>
-      </c>
-      <c r="O137" s="14">
-        <v>0</v>
-      </c>
-      <c r="P137" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q137" s="12">
+      <c r="G138" s="14">
+        <v>0</v>
+      </c>
+      <c r="H138" s="12">
+        <v>0</v>
+      </c>
+      <c r="I138" s="12">
+        <v>0</v>
+      </c>
+      <c r="J138" s="12">
+        <v>0</v>
+      </c>
+      <c r="K138" s="12">
+        <v>0</v>
+      </c>
+      <c r="L138" s="12">
+        <v>0</v>
+      </c>
+      <c r="M138" s="14">
+        <v>0</v>
+      </c>
+      <c r="N138" s="14">
+        <v>0</v>
+      </c>
+      <c r="O138" s="14">
+        <v>0</v>
+      </c>
+      <c r="P138" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q138" s="12">
         <v>0.05</v>
       </c>
-      <c r="R137" s="12">
-        <v>0</v>
-      </c>
-      <c r="S137" s="12">
-        <v>0</v>
-      </c>
-      <c r="T137" s="12">
-        <v>0</v>
-      </c>
-      <c r="U137" s="12">
-        <v>0</v>
-      </c>
-      <c r="V137" s="12">
-        <v>0</v>
-      </c>
-      <c r="W137" s="12">
-        <v>0</v>
-      </c>
-      <c r="X137" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y137" s="12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C138" s="12">
-        <v>300011</v>
-      </c>
-      <c r="D138" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="E138" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="F138" s="22" t="s">
-        <v>286</v>
-      </c>
-      <c r="G138" s="14">
-        <v>0</v>
-      </c>
-      <c r="H138" s="12">
-        <v>0</v>
-      </c>
-      <c r="I138" s="12">
-        <v>0</v>
-      </c>
-      <c r="J138" s="12">
-        <v>0</v>
-      </c>
-      <c r="K138" s="12">
-        <v>0</v>
-      </c>
-      <c r="L138" s="12">
-        <v>0</v>
-      </c>
-      <c r="M138" s="14">
-        <v>0</v>
-      </c>
-      <c r="N138" s="14">
-        <v>0</v>
-      </c>
-      <c r="O138" s="14">
-        <v>0</v>
-      </c>
-      <c r="P138" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q138" s="12">
-        <v>0</v>
-      </c>
       <c r="R138" s="12">
         <v>0</v>
       </c>
@@ -13084,22 +13108,22 @@
       <c r="X138" s="12">
         <v>0</v>
       </c>
-      <c r="Y138" s="12" t="s">
-        <v>194</v>
+      <c r="Y138" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C139" s="12">
-        <v>300012</v>
-      </c>
-      <c r="D139" s="21" t="s">
-        <v>182</v>
+      <c r="C139" s="17">
+        <v>190113</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E139" s="13" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="F139" s="22" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="G139" s="14">
         <v>0</v>
@@ -13156,21 +13180,21 @@
         <v>0</v>
       </c>
       <c r="Y139" s="12" t="s">
-        <v>195</v>
+        <v>174</v>
       </c>
     </row>
     <row r="140" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C140" s="12">
-        <v>300013</v>
-      </c>
-      <c r="D140" s="21" t="s">
-        <v>182</v>
+      <c r="C140" s="17">
+        <v>190121</v>
+      </c>
+      <c r="D140" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E140" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="F140" s="22" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="G140" s="14">
         <v>0</v>
@@ -13203,7 +13227,7 @@
         <v>0</v>
       </c>
       <c r="Q140" s="12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R140" s="12">
         <v>0</v>
@@ -13226,22 +13250,22 @@
       <c r="X140" s="12">
         <v>0</v>
       </c>
-      <c r="Y140" s="12">
-        <v>0</v>
+      <c r="Y140" s="20" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="141" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C141" s="12">
-        <v>300021</v>
-      </c>
-      <c r="D141" s="21" t="s">
-        <v>182</v>
+      <c r="C141" s="17">
+        <v>190122</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E141" s="13" t="s">
-        <v>187</v>
+        <v>140</v>
       </c>
       <c r="F141" s="22" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="G141" s="14">
         <v>0</v>
@@ -13274,7 +13298,7 @@
         <v>0</v>
       </c>
       <c r="Q141" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R141" s="12">
         <v>0</v>
@@ -13297,22 +13321,22 @@
       <c r="X141" s="12">
         <v>0</v>
       </c>
-      <c r="Y141" s="12" t="s">
-        <v>193</v>
+      <c r="Y141" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C142" s="12">
-        <v>300022</v>
-      </c>
-      <c r="D142" s="21" t="s">
-        <v>182</v>
+      <c r="C142" s="17">
+        <v>190123</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E142" s="13" t="s">
-        <v>188</v>
+        <v>150</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="G142" s="14">
         <v>0</v>
@@ -13354,7 +13378,7 @@
         <v>0</v>
       </c>
       <c r="T142" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="U142" s="12">
         <v>0</v>
@@ -13368,22 +13392,22 @@
       <c r="X142" s="12">
         <v>0</v>
       </c>
-      <c r="Y142" s="12" t="s">
-        <v>192</v>
+      <c r="Y142" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C143" s="12">
-        <v>300023</v>
-      </c>
-      <c r="D143" s="21" t="s">
-        <v>182</v>
+      <c r="C143" s="17">
+        <v>190131</v>
+      </c>
+      <c r="D143" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>186</v>
+        <v>324</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>290</v>
+        <v>325</v>
       </c>
       <c r="G143" s="14">
         <v>0</v>
@@ -13419,7 +13443,7 @@
         <v>0</v>
       </c>
       <c r="R143" s="12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="S143" s="12">
         <v>0</v>
@@ -13439,22 +13463,22 @@
       <c r="X143" s="12">
         <v>0</v>
       </c>
-      <c r="Y143" s="12">
-        <v>0</v>
+      <c r="Y143" s="20" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="144" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C144" s="12">
-        <v>300031</v>
-      </c>
-      <c r="D144" s="21" t="s">
-        <v>182</v>
+      <c r="C144" s="17">
+        <v>190132</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E144" s="13" t="s">
-        <v>190</v>
+        <v>169</v>
       </c>
       <c r="F144" s="22" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="G144" s="14">
         <v>0</v>
@@ -13493,7 +13517,7 @@
         <v>0</v>
       </c>
       <c r="S144" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="T144" s="12">
         <v>0</v>
@@ -13515,17 +13539,17 @@
       </c>
     </row>
     <row r="145" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="C145" s="12">
-        <v>300032</v>
-      </c>
-      <c r="D145" s="21" t="s">
-        <v>182</v>
+      <c r="C145" s="17">
+        <v>190133</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="E145" s="13" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="F145" s="22" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="G145" s="14">
         <v>0</v>
@@ -13537,7 +13561,7 @@
         <v>0</v>
       </c>
       <c r="J145" s="12">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K145" s="12">
         <v>0</v>
@@ -13561,7 +13585,7 @@
         <v>0</v>
       </c>
       <c r="R145" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="S145" s="12">
         <v>0</v>
@@ -13582,21 +13606,21 @@
         <v>0</v>
       </c>
       <c r="Y145" s="12" t="s">
-        <v>196</v>
+        <v>180</v>
       </c>
     </row>
     <row r="146" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C146" s="12">
-        <v>300033</v>
-      </c>
-      <c r="D146" s="21" t="s">
-        <v>182</v>
+        <v>200001</v>
+      </c>
+      <c r="D146" s="12" t="s">
+        <v>181</v>
       </c>
       <c r="E146" s="13" t="s">
-        <v>189</v>
+        <v>140</v>
       </c>
       <c r="F146" s="22" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="G146" s="14">
         <v>0</v>
@@ -13629,13 +13653,13 @@
         <v>0</v>
       </c>
       <c r="Q146" s="12">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R146" s="12">
         <v>0</v>
       </c>
       <c r="S146" s="12">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="T146" s="12">
         <v>0</v>
@@ -13658,16 +13682,16 @@
     </row>
     <row r="147" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C147" s="12">
-        <v>300111</v>
+        <v>300011</v>
       </c>
       <c r="D147" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E147" s="13" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="F147" s="22" t="s">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="G147" s="14">
         <v>0</v>
@@ -13724,21 +13748,21 @@
         <v>0</v>
       </c>
       <c r="Y147" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="148" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C148" s="12">
-        <v>300112</v>
+        <v>300012</v>
       </c>
       <c r="D148" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E148" s="13" t="s">
-        <v>203</v>
+        <v>185</v>
       </c>
       <c r="F148" s="22" t="s">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="G148" s="14">
         <v>0</v>
@@ -13795,21 +13819,21 @@
         <v>0</v>
       </c>
       <c r="Y148" s="12" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="149" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C149" s="12">
-        <v>300113</v>
+        <v>300013</v>
       </c>
       <c r="D149" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E149" s="13" t="s">
-        <v>204</v>
+        <v>183</v>
       </c>
       <c r="F149" s="22" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="G149" s="14">
         <v>0</v>
@@ -13842,7 +13866,7 @@
         <v>0</v>
       </c>
       <c r="Q149" s="12">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="R149" s="12">
         <v>0</v>
@@ -13871,16 +13895,16 @@
     </row>
     <row r="150" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C150" s="12">
-        <v>300121</v>
+        <v>300021</v>
       </c>
       <c r="D150" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E150" s="13" t="s">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="F150" s="22" t="s">
-        <v>305</v>
+        <v>289</v>
       </c>
       <c r="G150" s="14">
         <v>0</v>
@@ -13937,21 +13961,21 @@
         <v>0</v>
       </c>
       <c r="Y150" s="12" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="151" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C151" s="12">
-        <v>300122</v>
+        <v>300022</v>
       </c>
       <c r="D151" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E151" s="13" t="s">
-        <v>206</v>
+        <v>188</v>
       </c>
       <c r="F151" s="22" t="s">
-        <v>306</v>
+        <v>244</v>
       </c>
       <c r="G151" s="14">
         <v>0</v>
@@ -14008,21 +14032,21 @@
         <v>0</v>
       </c>
       <c r="Y151" s="12" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
     </row>
     <row r="152" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C152" s="12">
-        <v>300123</v>
+        <v>300023</v>
       </c>
       <c r="D152" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E152" s="13" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F152" s="22" t="s">
-        <v>307</v>
+        <v>290</v>
       </c>
       <c r="G152" s="14">
         <v>0</v>
@@ -14058,7 +14082,7 @@
         <v>0</v>
       </c>
       <c r="R152" s="12">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="S152" s="12">
         <v>0</v>
@@ -14084,16 +14108,16 @@
     </row>
     <row r="153" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C153" s="12">
-        <v>300131</v>
+        <v>300031</v>
       </c>
       <c r="D153" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E153" s="13" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="F153" s="22" t="s">
-        <v>308</v>
+        <v>291</v>
       </c>
       <c r="G153" s="14">
         <v>0</v>
@@ -14155,16 +14179,16 @@
     </row>
     <row r="154" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C154" s="12">
-        <v>300132</v>
+        <v>300032</v>
       </c>
       <c r="D154" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E154" s="13" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="F154" s="22" t="s">
-        <v>309</v>
+        <v>292</v>
       </c>
       <c r="G154" s="14">
         <v>0</v>
@@ -14221,21 +14245,21 @@
         <v>0</v>
       </c>
       <c r="Y154" s="12" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="155" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C155" s="12">
-        <v>300133</v>
+        <v>300033</v>
       </c>
       <c r="D155" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E155" s="13" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="F155" s="22" t="s">
-        <v>310</v>
+        <v>293</v>
       </c>
       <c r="G155" s="14">
         <v>0</v>
@@ -14274,7 +14298,7 @@
         <v>0</v>
       </c>
       <c r="S155" s="12">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="T155" s="12">
         <v>0</v>
@@ -14297,16 +14321,16 @@
     </row>
     <row r="156" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C156" s="12">
-        <v>300211</v>
+        <v>300111</v>
       </c>
       <c r="D156" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E156" s="13" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="F156" s="22" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="G156" s="14">
         <v>0</v>
@@ -14363,21 +14387,21 @@
         <v>0</v>
       </c>
       <c r="Y156" s="12" t="s">
-        <v>220</v>
+        <v>197</v>
       </c>
     </row>
     <row r="157" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C157" s="12">
-        <v>300212</v>
+        <v>300112</v>
       </c>
       <c r="D157" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E157" s="13" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F157" s="22" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="G157" s="14">
         <v>0</v>
@@ -14434,21 +14458,21 @@
         <v>0</v>
       </c>
       <c r="Y157" s="12" t="s">
-        <v>221</v>
+        <v>198</v>
       </c>
     </row>
     <row r="158" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C158" s="12">
-        <v>300213</v>
+        <v>300113</v>
       </c>
       <c r="D158" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E158" s="13" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="F158" s="22" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="G158" s="14">
         <v>0</v>
@@ -14481,7 +14505,7 @@
         <v>0</v>
       </c>
       <c r="Q158" s="12">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="R158" s="12">
         <v>0</v>
@@ -14510,16 +14534,16 @@
     </row>
     <row r="159" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C159" s="12">
-        <v>300221</v>
+        <v>300121</v>
       </c>
       <c r="D159" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E159" s="13" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F159" s="22" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="G159" s="14">
         <v>0</v>
@@ -14576,21 +14600,21 @@
         <v>0</v>
       </c>
       <c r="Y159" s="12" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
     </row>
     <row r="160" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C160" s="12">
-        <v>300222</v>
+        <v>300122</v>
       </c>
       <c r="D160" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E160" s="13" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="F160" s="22" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="G160" s="14">
         <v>0</v>
@@ -14647,21 +14671,21 @@
         <v>0</v>
       </c>
       <c r="Y160" s="12" t="s">
-        <v>223</v>
+        <v>200</v>
       </c>
     </row>
     <row r="161" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C161" s="12">
-        <v>300223</v>
+        <v>300123</v>
       </c>
       <c r="D161" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E161" s="13" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F161" s="22" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="G161" s="14">
         <v>0</v>
@@ -14697,7 +14721,7 @@
         <v>0</v>
       </c>
       <c r="R161" s="12">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="S161" s="12">
         <v>0</v>
@@ -14723,16 +14747,16 @@
     </row>
     <row r="162" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C162" s="12">
-        <v>300231</v>
+        <v>300131</v>
       </c>
       <c r="D162" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E162" s="13" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F162" s="22" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="G162" s="14">
         <v>0</v>
@@ -14794,16 +14818,16 @@
     </row>
     <row r="163" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C163" s="12">
-        <v>300232</v>
+        <v>300132</v>
       </c>
       <c r="D163" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E163" s="13" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="G163" s="14">
         <v>0</v>
@@ -14860,21 +14884,21 @@
         <v>0</v>
       </c>
       <c r="Y163" s="12" t="s">
-        <v>224</v>
+        <v>201</v>
       </c>
     </row>
     <row r="164" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C164" s="12">
-        <v>300233</v>
+        <v>300133</v>
       </c>
       <c r="D164" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E164" s="13" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F164" s="22" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="G164" s="14">
         <v>0</v>
@@ -14913,7 +14937,7 @@
         <v>0</v>
       </c>
       <c r="S164" s="12">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="T164" s="12">
         <v>0</v>
@@ -14936,16 +14960,16 @@
     </row>
     <row r="165" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C165" s="12">
-        <v>300311</v>
+        <v>300211</v>
       </c>
       <c r="D165" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E165" s="13" t="s">
-        <v>229</v>
+        <v>211</v>
       </c>
       <c r="F165" s="22" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="G165" s="14">
         <v>0</v>
@@ -15002,21 +15026,21 @@
         <v>0</v>
       </c>
       <c r="Y165" s="12" t="s">
-        <v>233</v>
+        <v>220</v>
       </c>
     </row>
     <row r="166" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C166" s="12">
-        <v>300312</v>
+        <v>300212</v>
       </c>
       <c r="D166" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E166" s="13" t="s">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="F166" s="22" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="G166" s="14">
         <v>0</v>
@@ -15073,21 +15097,21 @@
         <v>0</v>
       </c>
       <c r="Y166" s="12" t="s">
-        <v>234</v>
+        <v>221</v>
       </c>
     </row>
     <row r="167" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C167" s="12">
-        <v>300313</v>
+        <v>300213</v>
       </c>
       <c r="D167" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E167" s="13" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F167" s="22" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G167" s="14">
         <v>0</v>
@@ -15120,13 +15144,13 @@
         <v>0</v>
       </c>
       <c r="Q167" s="12">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R167" s="12">
         <v>0</v>
       </c>
       <c r="S167" s="12">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="T167" s="12">
         <v>0</v>
@@ -15149,16 +15173,16 @@
     </row>
     <row r="168" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C168" s="12">
-        <v>300321</v>
+        <v>300221</v>
       </c>
       <c r="D168" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E168" s="13" t="s">
-        <v>238</v>
+        <v>214</v>
       </c>
       <c r="F168" s="22" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
       <c r="G168" s="14">
         <v>0</v>
@@ -15215,21 +15239,21 @@
         <v>0</v>
       </c>
       <c r="Y168" s="12" t="s">
-        <v>235</v>
+        <v>222</v>
       </c>
     </row>
     <row r="169" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C169" s="12">
-        <v>300322</v>
+        <v>300222</v>
       </c>
       <c r="D169" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E169" s="13" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>246</v>
+        <v>315</v>
       </c>
       <c r="G169" s="14">
         <v>0</v>
@@ -15286,21 +15310,21 @@
         <v>0</v>
       </c>
       <c r="Y169" s="12" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
     </row>
     <row r="170" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C170" s="12">
-        <v>300323</v>
+        <v>300223</v>
       </c>
       <c r="D170" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E170" s="13" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="G170" s="14">
         <v>0</v>
@@ -15336,7 +15360,7 @@
         <v>0</v>
       </c>
       <c r="R170" s="12">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="S170" s="12">
         <v>0</v>
@@ -15356,22 +15380,22 @@
       <c r="X170" s="12">
         <v>0</v>
       </c>
-      <c r="Y170" s="12" t="s">
-        <v>224</v>
+      <c r="Y170" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="171" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C171" s="12">
-        <v>300331</v>
+        <v>300231</v>
       </c>
       <c r="D171" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E171" s="13" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F171" s="22" t="s">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="G171" s="14">
         <v>0</v>
@@ -15427,22 +15451,22 @@
       <c r="X171" s="12">
         <v>0</v>
       </c>
-      <c r="Y171" s="12" t="s">
-        <v>239</v>
+      <c r="Y171" s="12">
+        <v>0</v>
       </c>
     </row>
     <row r="172" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C172" s="12">
-        <v>300332</v>
+        <v>300232</v>
       </c>
       <c r="D172" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E172" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="G172" s="14">
         <v>0</v>
@@ -15499,96 +15523,735 @@
         <v>0</v>
       </c>
       <c r="Y172" s="12" t="s">
-        <v>237</v>
+        <v>224</v>
       </c>
     </row>
     <row r="173" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C173" s="12">
-        <v>300333</v>
+        <v>300233</v>
       </c>
       <c r="D173" s="21" t="s">
         <v>182</v>
       </c>
       <c r="E173" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F173" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="G173" s="14">
+        <v>0</v>
+      </c>
+      <c r="H173" s="12">
+        <v>0</v>
+      </c>
+      <c r="I173" s="12">
+        <v>0</v>
+      </c>
+      <c r="J173" s="12">
+        <v>0</v>
+      </c>
+      <c r="K173" s="12">
+        <v>0</v>
+      </c>
+      <c r="L173" s="12">
+        <v>0</v>
+      </c>
+      <c r="M173" s="14">
+        <v>0</v>
+      </c>
+      <c r="N173" s="14">
+        <v>0</v>
+      </c>
+      <c r="O173" s="14">
+        <v>0</v>
+      </c>
+      <c r="P173" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q173" s="12">
+        <v>0</v>
+      </c>
+      <c r="R173" s="12">
+        <v>0</v>
+      </c>
+      <c r="S173" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="T173" s="12">
+        <v>0</v>
+      </c>
+      <c r="U173" s="12">
+        <v>0</v>
+      </c>
+      <c r="V173" s="12">
+        <v>0</v>
+      </c>
+      <c r="W173" s="12">
+        <v>0</v>
+      </c>
+      <c r="X173" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y173" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C174" s="12">
+        <v>300311</v>
+      </c>
+      <c r="D174" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E174" s="13" t="s">
+        <v>229</v>
+      </c>
+      <c r="F174" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="G174" s="14">
+        <v>0</v>
+      </c>
+      <c r="H174" s="12">
+        <v>0</v>
+      </c>
+      <c r="I174" s="12">
+        <v>0</v>
+      </c>
+      <c r="J174" s="12">
+        <v>0</v>
+      </c>
+      <c r="K174" s="12">
+        <v>0</v>
+      </c>
+      <c r="L174" s="12">
+        <v>0</v>
+      </c>
+      <c r="M174" s="14">
+        <v>0</v>
+      </c>
+      <c r="N174" s="14">
+        <v>0</v>
+      </c>
+      <c r="O174" s="14">
+        <v>0</v>
+      </c>
+      <c r="P174" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q174" s="12">
+        <v>0</v>
+      </c>
+      <c r="R174" s="12">
+        <v>0</v>
+      </c>
+      <c r="S174" s="12">
+        <v>0</v>
+      </c>
+      <c r="T174" s="12">
+        <v>0</v>
+      </c>
+      <c r="U174" s="12">
+        <v>0</v>
+      </c>
+      <c r="V174" s="12">
+        <v>0</v>
+      </c>
+      <c r="W174" s="12">
+        <v>0</v>
+      </c>
+      <c r="X174" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y174" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="175" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C175" s="12">
+        <v>300312</v>
+      </c>
+      <c r="D175" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E175" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="F175" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="G175" s="14">
+        <v>0</v>
+      </c>
+      <c r="H175" s="12">
+        <v>0</v>
+      </c>
+      <c r="I175" s="12">
+        <v>0</v>
+      </c>
+      <c r="J175" s="12">
+        <v>0</v>
+      </c>
+      <c r="K175" s="12">
+        <v>0</v>
+      </c>
+      <c r="L175" s="12">
+        <v>0</v>
+      </c>
+      <c r="M175" s="14">
+        <v>0</v>
+      </c>
+      <c r="N175" s="14">
+        <v>0</v>
+      </c>
+      <c r="O175" s="14">
+        <v>0</v>
+      </c>
+      <c r="P175" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q175" s="12">
+        <v>0</v>
+      </c>
+      <c r="R175" s="12">
+        <v>0</v>
+      </c>
+      <c r="S175" s="12">
+        <v>0</v>
+      </c>
+      <c r="T175" s="12">
+        <v>0</v>
+      </c>
+      <c r="U175" s="12">
+        <v>0</v>
+      </c>
+      <c r="V175" s="12">
+        <v>0</v>
+      </c>
+      <c r="W175" s="12">
+        <v>0</v>
+      </c>
+      <c r="X175" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y175" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="176" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C176" s="12">
+        <v>300313</v>
+      </c>
+      <c r="D176" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E176" s="13" t="s">
+        <v>219</v>
+      </c>
+      <c r="F176" s="22" t="s">
+        <v>319</v>
+      </c>
+      <c r="G176" s="14">
+        <v>0</v>
+      </c>
+      <c r="H176" s="12">
+        <v>0</v>
+      </c>
+      <c r="I176" s="12">
+        <v>0</v>
+      </c>
+      <c r="J176" s="12">
+        <v>0</v>
+      </c>
+      <c r="K176" s="12">
+        <v>0</v>
+      </c>
+      <c r="L176" s="12">
+        <v>0</v>
+      </c>
+      <c r="M176" s="14">
+        <v>0</v>
+      </c>
+      <c r="N176" s="14">
+        <v>0</v>
+      </c>
+      <c r="O176" s="14">
+        <v>0</v>
+      </c>
+      <c r="P176" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q176" s="12">
+        <v>0</v>
+      </c>
+      <c r="R176" s="12">
+        <v>0</v>
+      </c>
+      <c r="S176" s="12">
+        <v>0.02</v>
+      </c>
+      <c r="T176" s="12">
+        <v>0</v>
+      </c>
+      <c r="U176" s="12">
+        <v>0</v>
+      </c>
+      <c r="V176" s="12">
+        <v>0</v>
+      </c>
+      <c r="W176" s="12">
+        <v>0</v>
+      </c>
+      <c r="X176" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C177" s="12">
+        <v>300321</v>
+      </c>
+      <c r="D177" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E177" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="F177" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="G177" s="14">
+        <v>0</v>
+      </c>
+      <c r="H177" s="12">
+        <v>0</v>
+      </c>
+      <c r="I177" s="12">
+        <v>0</v>
+      </c>
+      <c r="J177" s="12">
+        <v>0</v>
+      </c>
+      <c r="K177" s="12">
+        <v>0</v>
+      </c>
+      <c r="L177" s="12">
+        <v>0</v>
+      </c>
+      <c r="M177" s="14">
+        <v>0</v>
+      </c>
+      <c r="N177" s="14">
+        <v>0</v>
+      </c>
+      <c r="O177" s="14">
+        <v>0</v>
+      </c>
+      <c r="P177" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q177" s="12">
+        <v>0</v>
+      </c>
+      <c r="R177" s="12">
+        <v>0</v>
+      </c>
+      <c r="S177" s="12">
+        <v>0</v>
+      </c>
+      <c r="T177" s="12">
+        <v>0</v>
+      </c>
+      <c r="U177" s="12">
+        <v>0</v>
+      </c>
+      <c r="V177" s="12">
+        <v>0</v>
+      </c>
+      <c r="W177" s="12">
+        <v>0</v>
+      </c>
+      <c r="X177" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y177" s="12" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="178" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C178" s="12">
+        <v>300322</v>
+      </c>
+      <c r="D178" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E178" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F178" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="G178" s="14">
+        <v>0</v>
+      </c>
+      <c r="H178" s="12">
+        <v>0</v>
+      </c>
+      <c r="I178" s="12">
+        <v>0</v>
+      </c>
+      <c r="J178" s="12">
+        <v>0</v>
+      </c>
+      <c r="K178" s="12">
+        <v>0</v>
+      </c>
+      <c r="L178" s="12">
+        <v>0</v>
+      </c>
+      <c r="M178" s="14">
+        <v>0</v>
+      </c>
+      <c r="N178" s="14">
+        <v>0</v>
+      </c>
+      <c r="O178" s="14">
+        <v>0</v>
+      </c>
+      <c r="P178" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q178" s="12">
+        <v>0</v>
+      </c>
+      <c r="R178" s="12">
+        <v>0</v>
+      </c>
+      <c r="S178" s="12">
+        <v>0</v>
+      </c>
+      <c r="T178" s="12">
+        <v>0</v>
+      </c>
+      <c r="U178" s="12">
+        <v>0</v>
+      </c>
+      <c r="V178" s="12">
+        <v>0</v>
+      </c>
+      <c r="W178" s="12">
+        <v>0</v>
+      </c>
+      <c r="X178" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y178" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="179" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C179" s="12">
+        <v>300323</v>
+      </c>
+      <c r="D179" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E179" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="F173" s="22" t="s">
+      <c r="F179" s="22" t="s">
         <v>318</v>
       </c>
-      <c r="G173" s="14">
-        <v>0</v>
-      </c>
-      <c r="H173" s="12">
-        <v>0</v>
-      </c>
-      <c r="I173" s="12">
-        <v>0</v>
-      </c>
-      <c r="J173" s="12">
-        <v>0</v>
-      </c>
-      <c r="K173" s="12">
-        <v>0</v>
-      </c>
-      <c r="L173" s="12">
-        <v>0</v>
-      </c>
-      <c r="M173" s="14">
-        <v>0</v>
-      </c>
-      <c r="N173" s="14">
-        <v>0</v>
-      </c>
-      <c r="O173" s="14">
-        <v>0</v>
-      </c>
-      <c r="P173" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q173" s="12">
-        <v>0</v>
-      </c>
-      <c r="R173" s="12">
-        <v>0</v>
-      </c>
-      <c r="S173" s="12">
-        <v>0</v>
-      </c>
-      <c r="T173" s="12">
-        <v>0</v>
-      </c>
-      <c r="U173" s="12">
-        <v>0</v>
-      </c>
-      <c r="V173" s="12">
-        <v>0</v>
-      </c>
-      <c r="W173" s="12">
-        <v>0</v>
-      </c>
-      <c r="X173" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y173" s="12" t="s">
+      <c r="G179" s="14">
+        <v>0</v>
+      </c>
+      <c r="H179" s="12">
+        <v>0</v>
+      </c>
+      <c r="I179" s="12">
+        <v>0</v>
+      </c>
+      <c r="J179" s="12">
+        <v>0</v>
+      </c>
+      <c r="K179" s="12">
+        <v>0</v>
+      </c>
+      <c r="L179" s="12">
+        <v>0</v>
+      </c>
+      <c r="M179" s="14">
+        <v>0</v>
+      </c>
+      <c r="N179" s="14">
+        <v>0</v>
+      </c>
+      <c r="O179" s="14">
+        <v>0</v>
+      </c>
+      <c r="P179" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q179" s="12">
+        <v>0</v>
+      </c>
+      <c r="R179" s="12">
+        <v>0</v>
+      </c>
+      <c r="S179" s="12">
+        <v>0</v>
+      </c>
+      <c r="T179" s="12">
+        <v>0</v>
+      </c>
+      <c r="U179" s="12">
+        <v>0</v>
+      </c>
+      <c r="V179" s="12">
+        <v>0</v>
+      </c>
+      <c r="W179" s="12">
+        <v>0</v>
+      </c>
+      <c r="X179" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="12" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="174" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C180" s="12">
+        <v>300331</v>
+      </c>
+      <c r="D180" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E180" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="F180" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="G180" s="14">
+        <v>0</v>
+      </c>
+      <c r="H180" s="12">
+        <v>0</v>
+      </c>
+      <c r="I180" s="12">
+        <v>0</v>
+      </c>
+      <c r="J180" s="12">
+        <v>0</v>
+      </c>
+      <c r="K180" s="12">
+        <v>0</v>
+      </c>
+      <c r="L180" s="12">
+        <v>0</v>
+      </c>
+      <c r="M180" s="14">
+        <v>0</v>
+      </c>
+      <c r="N180" s="14">
+        <v>0</v>
+      </c>
+      <c r="O180" s="14">
+        <v>0</v>
+      </c>
+      <c r="P180" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q180" s="12">
+        <v>0</v>
+      </c>
+      <c r="R180" s="12">
+        <v>0</v>
+      </c>
+      <c r="S180" s="12">
+        <v>0</v>
+      </c>
+      <c r="T180" s="12">
+        <v>0</v>
+      </c>
+      <c r="U180" s="12">
+        <v>0</v>
+      </c>
+      <c r="V180" s="12">
+        <v>0</v>
+      </c>
+      <c r="W180" s="12">
+        <v>0</v>
+      </c>
+      <c r="X180" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="181" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C181" s="12">
+        <v>300332</v>
+      </c>
+      <c r="D181" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E181" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="F181" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="G181" s="14">
+        <v>0</v>
+      </c>
+      <c r="H181" s="12">
+        <v>0</v>
+      </c>
+      <c r="I181" s="12">
+        <v>0</v>
+      </c>
+      <c r="J181" s="12">
+        <v>0</v>
+      </c>
+      <c r="K181" s="12">
+        <v>0</v>
+      </c>
+      <c r="L181" s="12">
+        <v>0</v>
+      </c>
+      <c r="M181" s="14">
+        <v>0</v>
+      </c>
+      <c r="N181" s="14">
+        <v>0</v>
+      </c>
+      <c r="O181" s="14">
+        <v>0</v>
+      </c>
+      <c r="P181" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q181" s="12">
+        <v>0</v>
+      </c>
+      <c r="R181" s="12">
+        <v>0</v>
+      </c>
+      <c r="S181" s="12">
+        <v>0</v>
+      </c>
+      <c r="T181" s="12">
+        <v>0</v>
+      </c>
+      <c r="U181" s="12">
+        <v>0</v>
+      </c>
+      <c r="V181" s="12">
+        <v>0</v>
+      </c>
+      <c r="W181" s="12">
+        <v>0</v>
+      </c>
+      <c r="X181" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y181" s="12" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="182" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C182" s="12">
+        <v>300333</v>
+      </c>
+      <c r="D182" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E182" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="F182" s="22" t="s">
+        <v>318</v>
+      </c>
+      <c r="G182" s="14">
+        <v>0</v>
+      </c>
+      <c r="H182" s="12">
+        <v>0</v>
+      </c>
+      <c r="I182" s="12">
+        <v>0</v>
+      </c>
+      <c r="J182" s="12">
+        <v>0</v>
+      </c>
+      <c r="K182" s="12">
+        <v>0</v>
+      </c>
+      <c r="L182" s="12">
+        <v>0</v>
+      </c>
+      <c r="M182" s="14">
+        <v>0</v>
+      </c>
+      <c r="N182" s="14">
+        <v>0</v>
+      </c>
+      <c r="O182" s="14">
+        <v>0</v>
+      </c>
+      <c r="P182" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q182" s="12">
+        <v>0</v>
+      </c>
+      <c r="R182" s="12">
+        <v>0</v>
+      </c>
+      <c r="S182" s="12">
+        <v>0</v>
+      </c>
+      <c r="T182" s="12">
+        <v>0</v>
+      </c>
+      <c r="U182" s="12">
+        <v>0</v>
+      </c>
+      <c r="V182" s="12">
+        <v>0</v>
+      </c>
+      <c r="W182" s="12">
+        <v>0</v>
+      </c>
+      <c r="X182" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y182" s="12" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="183" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/EquipSuitPropertyConfig.xlsx
+++ b/Excel/EquipSuitPropertyConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF82666-A4C0-48B0-A9C8-5F318156E93D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53304B85-BF3E-4E94-A0F7-76A44F7D09AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipSuitPropertyProto" sheetId="1" r:id="rId1"/>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="353">
   <si>
     <t>Id</t>
   </si>
@@ -856,12 +856,6 @@
     <t>Attack +1%</t>
   </si>
   <si>
-    <t>Agility +20</t>
-  </si>
-  <si>
-    <t>Stamina +20</t>
-  </si>
-  <si>
     <t>Attack +20</t>
   </si>
   <si>
@@ -1003,15 +997,6 @@
     <t>Evasion +1%</t>
   </si>
   <si>
-    <t>Strength +20</t>
-  </si>
-  <si>
-    <t>Vitality +20</t>
-  </si>
-  <si>
-    <t>Intelligence +20</t>
-  </si>
-  <si>
     <t>Attack +50</t>
   </si>
   <si>
@@ -1036,49 +1021,10 @@
     <t>Crit +1.5%</t>
   </si>
   <si>
-    <t>Physical Def +1.5%</t>
-  </si>
-  <si>
-    <t>Attack +1.5%</t>
-  </si>
-  <si>
-    <t>Hit +1.5%</t>
-  </si>
-  <si>
-    <t>Crit Resistance +1.5%</t>
-  </si>
-  <si>
-    <t>HP +1.5%</t>
-  </si>
-  <si>
-    <t>Evasion +1.5%</t>
-  </si>
-  <si>
-    <t>Magic Def +2%</t>
-  </si>
-  <si>
-    <t>Spell Power +2%</t>
-  </si>
-  <si>
-    <t>Crit +2%</t>
-  </si>
-  <si>
-    <t>Physical Def +2%</t>
-  </si>
-  <si>
-    <t>Attack +2%</t>
-  </si>
-  <si>
-    <t>Hit +2%</t>
-  </si>
-  <si>
     <t>Crit Resistance +2%</t>
   </si>
   <si>
     <t>HP +2%</t>
-  </si>
-  <si>
-    <t>Evasion +2%</t>
   </si>
   <si>
     <t>110301,400</t>
@@ -1102,6 +1048,186 @@
   </si>
   <si>
     <t>Ignore Def +500</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量+30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏捷+30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>体质+30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力+30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>智力+30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗暴+3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>血量+3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP +3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>105103,30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>105203,30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>105503,30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>105403,30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>105303,30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>100202,0.03</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>200403,0.03</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit Rate +5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit Rate + 3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vitality + 30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina + 30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP + 3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intelligence + 30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crit Resistance + 3%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strength + 30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agility + 30</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Intelligence + 20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stamina + 20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vitality + 20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Agility + 20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Strength + 20</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crit Resistance + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical Def + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crit + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Spell Power + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic Def + 2%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Evasion + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>HP + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crit Resistance + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hit + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical Def + 1.5%</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中+3%</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -7230,7 +7356,7 @@
         <v>125</v>
       </c>
       <c r="F56" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G56" s="14">
         <v>0</v>
@@ -7301,7 +7427,7 @@
         <v>126</v>
       </c>
       <c r="F57" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G57" s="14">
         <v>0</v>
@@ -7372,7 +7498,7 @@
         <v>127</v>
       </c>
       <c r="F58" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G58" s="14">
         <v>0</v>
@@ -7443,7 +7569,7 @@
         <v>125</v>
       </c>
       <c r="F59" s="22" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G59" s="14">
         <v>0</v>
@@ -7514,7 +7640,7 @@
         <v>126</v>
       </c>
       <c r="F60" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G60" s="14">
         <v>0</v>
@@ -7585,7 +7711,7 @@
         <v>127</v>
       </c>
       <c r="F61" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G61" s="14">
         <v>0</v>
@@ -7656,7 +7782,7 @@
         <v>127</v>
       </c>
       <c r="F62" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G62" s="14">
         <v>0</v>
@@ -7727,7 +7853,7 @@
         <v>126</v>
       </c>
       <c r="F63" s="22" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="G63" s="14">
         <v>0</v>
@@ -7798,7 +7924,7 @@
         <v>127</v>
       </c>
       <c r="F64" s="22" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="G64" s="14">
         <v>0</v>
@@ -7869,7 +7995,7 @@
         <v>131</v>
       </c>
       <c r="F65" s="23" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G65" s="19">
         <v>0</v>
@@ -7940,7 +8066,7 @@
         <v>132</v>
       </c>
       <c r="F66" s="23" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G66" s="19">
         <v>0</v>
@@ -8011,7 +8137,7 @@
         <v>133</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="G67" s="19">
         <v>0</v>
@@ -8082,7 +8208,7 @@
         <v>134</v>
       </c>
       <c r="F68" s="23" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G68" s="19">
         <v>0</v>
@@ -8153,7 +8279,7 @@
         <v>132</v>
       </c>
       <c r="F69" s="23" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="G69" s="19">
         <v>0</v>
@@ -8224,7 +8350,7 @@
         <v>135</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G70" s="19">
         <v>0</v>
@@ -8295,7 +8421,7 @@
         <v>136</v>
       </c>
       <c r="F71" s="23" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="G71" s="19">
         <v>0</v>
@@ -8366,7 +8492,7 @@
         <v>137</v>
       </c>
       <c r="F72" s="23" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G72" s="19">
         <v>0</v>
@@ -8437,7 +8563,7 @@
         <v>138</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G73" s="19">
         <v>0</v>
@@ -8508,7 +8634,7 @@
         <v>240</v>
       </c>
       <c r="F74" s="23" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="G74" s="19">
         <v>0</v>
@@ -8579,7 +8705,7 @@
         <v>139</v>
       </c>
       <c r="F75" s="23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G75" s="19">
         <v>0</v>
@@ -8650,7 +8776,7 @@
         <v>140</v>
       </c>
       <c r="F76" s="23" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G76" s="19">
         <v>0</v>
@@ -8721,7 +8847,7 @@
         <v>141</v>
       </c>
       <c r="F77" s="23" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="G77" s="19">
         <v>0</v>
@@ -8792,7 +8918,7 @@
         <v>142</v>
       </c>
       <c r="F78" s="23" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G78" s="19">
         <v>0</v>
@@ -8863,7 +8989,7 @@
         <v>143</v>
       </c>
       <c r="F79" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G79" s="19">
         <v>0</v>
@@ -8934,7 +9060,7 @@
         <v>145</v>
       </c>
       <c r="F80" s="23" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G80" s="19">
         <v>0</v>
@@ -9005,7 +9131,7 @@
         <v>146</v>
       </c>
       <c r="F81" s="23" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G81" s="19">
         <v>0</v>
@@ -9076,7 +9202,7 @@
         <v>148</v>
       </c>
       <c r="F82" s="23" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G82" s="19">
         <v>0</v>
@@ -9147,7 +9273,7 @@
         <v>149</v>
       </c>
       <c r="F83" s="23" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G83" s="19">
         <v>0</v>
@@ -9218,7 +9344,7 @@
         <v>143</v>
       </c>
       <c r="F84" s="23" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="G84" s="19">
         <v>0</v>
@@ -9289,7 +9415,7 @@
         <v>150</v>
       </c>
       <c r="F85" s="23" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G85" s="19">
         <v>0</v>
@@ -9360,7 +9486,7 @@
         <v>151</v>
       </c>
       <c r="F86" s="23" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="G86" s="19">
         <v>0</v>
@@ -9431,7 +9557,7 @@
         <v>152</v>
       </c>
       <c r="F87" s="23" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G87" s="19">
         <v>0</v>
@@ -9502,7 +9628,7 @@
         <v>140</v>
       </c>
       <c r="F88" s="23" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G88" s="19">
         <v>0</v>
@@ -9573,7 +9699,7 @@
         <v>153</v>
       </c>
       <c r="F89" s="23" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="G89" s="19">
         <v>0</v>
@@ -9644,7 +9770,7 @@
         <v>154</v>
       </c>
       <c r="F90" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G90" s="19">
         <v>0</v>
@@ -9715,7 +9841,7 @@
         <v>155</v>
       </c>
       <c r="F91" s="23" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G91" s="19">
         <v>0</v>
@@ -9786,7 +9912,7 @@
         <v>156</v>
       </c>
       <c r="F92" s="23" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="G92" s="19">
         <v>0</v>
@@ -9857,7 +9983,7 @@
         <v>157</v>
       </c>
       <c r="F93" s="23" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G93" s="19">
         <v>0</v>
@@ -9928,7 +10054,7 @@
         <v>158</v>
       </c>
       <c r="F94" s="23" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G94" s="19">
         <v>0</v>
@@ -9999,7 +10125,7 @@
         <v>160</v>
       </c>
       <c r="F95" s="23" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="G95" s="19">
         <v>0</v>
@@ -10070,7 +10196,7 @@
         <v>161</v>
       </c>
       <c r="F96" s="22" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="G96" s="14">
         <v>0</v>
@@ -10141,7 +10267,7 @@
         <v>162</v>
       </c>
       <c r="F97" s="23" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G97" s="19">
         <v>0</v>
@@ -10212,7 +10338,7 @@
         <v>164</v>
       </c>
       <c r="F98" s="23" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G98" s="19">
         <v>0</v>
@@ -10283,7 +10409,7 @@
         <v>154</v>
       </c>
       <c r="F99" s="23" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G99" s="19">
         <v>0</v>
@@ -10354,7 +10480,7 @@
         <v>165</v>
       </c>
       <c r="F100" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G100" s="19">
         <v>0</v>
@@ -10425,7 +10551,7 @@
         <v>157</v>
       </c>
       <c r="F101" s="22" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G101" s="14">
         <v>0</v>
@@ -10496,7 +10622,7 @@
         <v>151</v>
       </c>
       <c r="F102" s="22" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G102" s="14">
         <v>0</v>
@@ -10567,7 +10693,7 @@
         <v>140</v>
       </c>
       <c r="F103" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G103" s="14">
         <v>0</v>
@@ -10638,7 +10764,7 @@
         <v>157</v>
       </c>
       <c r="F104" s="22" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G104" s="14">
         <v>0</v>
@@ -10709,7 +10835,7 @@
         <v>167</v>
       </c>
       <c r="F105" s="22" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G105" s="14">
         <v>0</v>
@@ -10780,7 +10906,7 @@
         <v>150</v>
       </c>
       <c r="F106" s="22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G106" s="14">
         <v>0</v>
@@ -10851,7 +10977,7 @@
         <v>168</v>
       </c>
       <c r="F107" s="22" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="G107" s="14">
         <v>0</v>
@@ -10922,7 +11048,7 @@
         <v>169</v>
       </c>
       <c r="F108" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G108" s="14">
         <v>0</v>
@@ -10993,7 +11119,7 @@
         <v>146</v>
       </c>
       <c r="F109" s="22" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="G109" s="14">
         <v>0</v>
@@ -11064,7 +11190,7 @@
         <v>171</v>
       </c>
       <c r="F110" s="22" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="G110" s="14">
         <v>0</v>
@@ -11135,7 +11261,7 @@
         <v>140</v>
       </c>
       <c r="F111" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G111" s="14">
         <v>0</v>
@@ -11206,7 +11332,7 @@
         <v>173</v>
       </c>
       <c r="F112" s="22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G112" s="14">
         <v>0</v>
@@ -11277,7 +11403,7 @@
         <v>175</v>
       </c>
       <c r="F113" s="22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G113" s="14">
         <v>0</v>
@@ -11348,7 +11474,7 @@
         <v>140</v>
       </c>
       <c r="F114" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G114" s="14">
         <v>0</v>
@@ -11419,7 +11545,7 @@
         <v>150</v>
       </c>
       <c r="F115" s="22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G115" s="14">
         <v>0</v>
@@ -11490,7 +11616,7 @@
         <v>177</v>
       </c>
       <c r="F116" s="22" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="G116" s="14">
         <v>0</v>
@@ -11561,7 +11687,7 @@
         <v>169</v>
       </c>
       <c r="F117" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G117" s="14">
         <v>0</v>
@@ -11632,7 +11758,7 @@
         <v>179</v>
       </c>
       <c r="F118" s="22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G118" s="14">
         <v>0</v>
@@ -11703,7 +11829,7 @@
         <v>225</v>
       </c>
       <c r="F119" s="22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G119" s="14">
         <v>0</v>
@@ -11774,7 +11900,7 @@
         <v>140</v>
       </c>
       <c r="F120" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G120" s="14">
         <v>0</v>
@@ -11845,7 +11971,7 @@
         <v>173</v>
       </c>
       <c r="F121" s="22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G121" s="14">
         <v>0</v>
@@ -11916,7 +12042,7 @@
         <v>175</v>
       </c>
       <c r="F122" s="22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G122" s="14">
         <v>0</v>
@@ -11987,7 +12113,7 @@
         <v>140</v>
       </c>
       <c r="F123" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G123" s="14">
         <v>0</v>
@@ -12058,7 +12184,7 @@
         <v>150</v>
       </c>
       <c r="F124" s="22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G124" s="14">
         <v>0</v>
@@ -12129,7 +12255,7 @@
         <v>226</v>
       </c>
       <c r="F125" s="22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G125" s="14">
         <v>0</v>
@@ -12200,7 +12326,7 @@
         <v>169</v>
       </c>
       <c r="F126" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G126" s="14">
         <v>0</v>
@@ -12271,7 +12397,7 @@
         <v>179</v>
       </c>
       <c r="F127" s="22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G127" s="14">
         <v>0</v>
@@ -12342,7 +12468,7 @@
         <v>225</v>
       </c>
       <c r="F128" s="22" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="G128" s="14">
         <v>0</v>
@@ -12413,7 +12539,7 @@
         <v>140</v>
       </c>
       <c r="F129" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G129" s="14">
         <v>0</v>
@@ -12484,7 +12610,7 @@
         <v>173</v>
       </c>
       <c r="F130" s="22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G130" s="14">
         <v>0</v>
@@ -12555,7 +12681,7 @@
         <v>175</v>
       </c>
       <c r="F131" s="22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G131" s="14">
         <v>0</v>
@@ -12626,7 +12752,7 @@
         <v>140</v>
       </c>
       <c r="F132" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G132" s="14">
         <v>0</v>
@@ -12697,7 +12823,7 @@
         <v>150</v>
       </c>
       <c r="F133" s="22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G133" s="14">
         <v>0</v>
@@ -12768,7 +12894,7 @@
         <v>226</v>
       </c>
       <c r="F134" s="22" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="G134" s="14">
         <v>0</v>
@@ -12825,7 +12951,7 @@
         <v>0</v>
       </c>
       <c r="Y134" s="20" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="135" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -12839,7 +12965,7 @@
         <v>169</v>
       </c>
       <c r="F135" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G135" s="14">
         <v>0</v>
@@ -12910,7 +13036,7 @@
         <v>179</v>
       </c>
       <c r="F136" s="22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G136" s="14">
         <v>0</v>
@@ -12978,10 +13104,10 @@
         <v>130</v>
       </c>
       <c r="E137" s="13" t="s">
-        <v>322</v>
+        <v>304</v>
       </c>
       <c r="F137" s="22" t="s">
-        <v>321</v>
+        <v>303</v>
       </c>
       <c r="G137" s="14">
         <v>0</v>
@@ -13038,7 +13164,7 @@
         <v>0</v>
       </c>
       <c r="Y137" s="20" t="s">
-        <v>320</v>
+        <v>302</v>
       </c>
     </row>
     <row r="138" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13052,7 +13178,7 @@
         <v>140</v>
       </c>
       <c r="F138" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G138" s="14">
         <v>0</v>
@@ -13123,7 +13249,7 @@
         <v>173</v>
       </c>
       <c r="F139" s="22" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G139" s="14">
         <v>0</v>
@@ -13194,7 +13320,7 @@
         <v>175</v>
       </c>
       <c r="F140" s="22" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="G140" s="14">
         <v>0</v>
@@ -13265,7 +13391,7 @@
         <v>140</v>
       </c>
       <c r="F141" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G141" s="14">
         <v>0</v>
@@ -13336,7 +13462,7 @@
         <v>150</v>
       </c>
       <c r="F142" s="22" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G142" s="14">
         <v>0</v>
@@ -13404,10 +13530,10 @@
         <v>130</v>
       </c>
       <c r="E143" s="13" t="s">
-        <v>324</v>
+        <v>306</v>
       </c>
       <c r="F143" s="22" t="s">
-        <v>325</v>
+        <v>307</v>
       </c>
       <c r="G143" s="14">
         <v>0</v>
@@ -13464,7 +13590,7 @@
         <v>0</v>
       </c>
       <c r="Y143" s="20" t="s">
-        <v>323</v>
+        <v>305</v>
       </c>
     </row>
     <row r="144" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
@@ -13478,7 +13604,7 @@
         <v>169</v>
       </c>
       <c r="F144" s="22" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="G144" s="14">
         <v>0</v>
@@ -13549,7 +13675,7 @@
         <v>179</v>
       </c>
       <c r="F145" s="22" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="G145" s="14">
         <v>0</v>
@@ -13620,7 +13746,7 @@
         <v>140</v>
       </c>
       <c r="F146" s="22" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G146" s="14">
         <v>0</v>
@@ -13691,7 +13817,7 @@
         <v>184</v>
       </c>
       <c r="F147" s="22" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="G147" s="14">
         <v>0</v>
@@ -13762,7 +13888,7 @@
         <v>185</v>
       </c>
       <c r="F148" s="22" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G148" s="14">
         <v>0</v>
@@ -13833,7 +13959,7 @@
         <v>183</v>
       </c>
       <c r="F149" s="22" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="G149" s="14">
         <v>0</v>
@@ -13904,7 +14030,7 @@
         <v>187</v>
       </c>
       <c r="F150" s="22" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G150" s="14">
         <v>0</v>
@@ -14046,7 +14172,7 @@
         <v>186</v>
       </c>
       <c r="F152" s="22" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="G152" s="14">
         <v>0</v>
@@ -14117,7 +14243,7 @@
         <v>190</v>
       </c>
       <c r="F153" s="22" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="G153" s="14">
         <v>0</v>
@@ -14188,7 +14314,7 @@
         <v>191</v>
       </c>
       <c r="F154" s="22" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="G154" s="14">
         <v>0</v>
@@ -14259,7 +14385,7 @@
         <v>189</v>
       </c>
       <c r="F155" s="22" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="G155" s="14">
         <v>0</v>
@@ -14330,7 +14456,7 @@
         <v>202</v>
       </c>
       <c r="F156" s="22" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="G156" s="14">
         <v>0</v>
@@ -14401,7 +14527,7 @@
         <v>203</v>
       </c>
       <c r="F157" s="22" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="G157" s="14">
         <v>0</v>
@@ -14472,7 +14598,7 @@
         <v>204</v>
       </c>
       <c r="F158" s="22" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="G158" s="14">
         <v>0</v>
@@ -14543,7 +14669,7 @@
         <v>205</v>
       </c>
       <c r="F159" s="22" t="s">
-        <v>305</v>
+        <v>351</v>
       </c>
       <c r="G159" s="14">
         <v>0</v>
@@ -14614,7 +14740,7 @@
         <v>206</v>
       </c>
       <c r="F160" s="22" t="s">
-        <v>306</v>
+        <v>350</v>
       </c>
       <c r="G160" s="14">
         <v>0</v>
@@ -14685,7 +14811,7 @@
         <v>207</v>
       </c>
       <c r="F161" s="22" t="s">
-        <v>307</v>
+        <v>349</v>
       </c>
       <c r="G161" s="14">
         <v>0</v>
@@ -14756,7 +14882,7 @@
         <v>208</v>
       </c>
       <c r="F162" s="22" t="s">
-        <v>308</v>
+        <v>348</v>
       </c>
       <c r="G162" s="14">
         <v>0</v>
@@ -14827,7 +14953,7 @@
         <v>209</v>
       </c>
       <c r="F163" s="22" t="s">
-        <v>309</v>
+        <v>347</v>
       </c>
       <c r="G163" s="14">
         <v>0</v>
@@ -14898,7 +15024,7 @@
         <v>210</v>
       </c>
       <c r="F164" s="22" t="s">
-        <v>310</v>
+        <v>346</v>
       </c>
       <c r="G164" s="14">
         <v>0</v>
@@ -14969,7 +15095,7 @@
         <v>211</v>
       </c>
       <c r="F165" s="22" t="s">
-        <v>311</v>
+        <v>345</v>
       </c>
       <c r="G165" s="14">
         <v>0</v>
@@ -15040,7 +15166,7 @@
         <v>212</v>
       </c>
       <c r="F166" s="22" t="s">
-        <v>312</v>
+        <v>344</v>
       </c>
       <c r="G166" s="14">
         <v>0</v>
@@ -15111,7 +15237,7 @@
         <v>213</v>
       </c>
       <c r="F167" s="22" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="G167" s="14">
         <v>0</v>
@@ -15182,7 +15308,7 @@
         <v>214</v>
       </c>
       <c r="F168" s="22" t="s">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="G168" s="14">
         <v>0</v>
@@ -15253,7 +15379,7 @@
         <v>215</v>
       </c>
       <c r="F169" s="22" t="s">
-        <v>315</v>
+        <v>341</v>
       </c>
       <c r="G169" s="14">
         <v>0</v>
@@ -15324,7 +15450,7 @@
         <v>216</v>
       </c>
       <c r="F170" s="22" t="s">
-        <v>316</v>
+        <v>340</v>
       </c>
       <c r="G170" s="14">
         <v>0</v>
@@ -15395,7 +15521,7 @@
         <v>217</v>
       </c>
       <c r="F171" s="22" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="G171" s="14">
         <v>0</v>
@@ -15466,7 +15592,7 @@
         <v>218</v>
       </c>
       <c r="F172" s="22" t="s">
-        <v>318</v>
+        <v>338</v>
       </c>
       <c r="G172" s="14">
         <v>0</v>
@@ -15537,7 +15663,7 @@
         <v>219</v>
       </c>
       <c r="F173" s="22" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="G173" s="14">
         <v>0</v>
@@ -15608,7 +15734,7 @@
         <v>229</v>
       </c>
       <c r="F174" s="22" t="s">
-        <v>294</v>
+        <v>337</v>
       </c>
       <c r="G174" s="14">
         <v>0</v>
@@ -15679,7 +15805,7 @@
         <v>230</v>
       </c>
       <c r="F175" s="22" t="s">
-        <v>245</v>
+        <v>335</v>
       </c>
       <c r="G175" s="14">
         <v>0</v>
@@ -15750,7 +15876,7 @@
         <v>219</v>
       </c>
       <c r="F176" s="22" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="G176" s="14">
         <v>0</v>
@@ -15821,7 +15947,7 @@
         <v>238</v>
       </c>
       <c r="F177" s="22" t="s">
-        <v>295</v>
+        <v>334</v>
       </c>
       <c r="G177" s="14">
         <v>0</v>
@@ -15892,7 +16018,7 @@
         <v>231</v>
       </c>
       <c r="F178" s="22" t="s">
-        <v>246</v>
+        <v>333</v>
       </c>
       <c r="G178" s="14">
         <v>0</v>
@@ -15963,7 +16089,7 @@
         <v>218</v>
       </c>
       <c r="F179" s="22" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="G179" s="14">
         <v>0</v>
@@ -16034,7 +16160,7 @@
         <v>232</v>
       </c>
       <c r="F180" s="22" t="s">
-        <v>296</v>
+        <v>332</v>
       </c>
       <c r="G180" s="14">
         <v>0</v>
@@ -16105,7 +16231,7 @@
         <v>217</v>
       </c>
       <c r="F181" s="22" t="s">
-        <v>317</v>
+        <v>300</v>
       </c>
       <c r="G181" s="14">
         <v>0</v>
@@ -16176,7 +16302,7 @@
         <v>218</v>
       </c>
       <c r="F182" s="22" t="s">
-        <v>318</v>
+        <v>301</v>
       </c>
       <c r="G182" s="14">
         <v>0</v>
@@ -16236,15 +16362,645 @@
         <v>224</v>
       </c>
     </row>
-    <row r="183" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C183" s="12">
+        <v>300411</v>
+      </c>
+      <c r="D183" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E183" s="13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F183" s="22" t="s">
+        <v>330</v>
+      </c>
+      <c r="G183" s="14">
+        <v>0</v>
+      </c>
+      <c r="H183" s="12">
+        <v>0</v>
+      </c>
+      <c r="I183" s="12">
+        <v>0</v>
+      </c>
+      <c r="J183" s="12">
+        <v>0</v>
+      </c>
+      <c r="K183" s="12">
+        <v>0</v>
+      </c>
+      <c r="L183" s="12">
+        <v>0</v>
+      </c>
+      <c r="M183" s="14">
+        <v>0</v>
+      </c>
+      <c r="N183" s="14">
+        <v>0</v>
+      </c>
+      <c r="O183" s="14">
+        <v>0</v>
+      </c>
+      <c r="P183" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q183" s="12">
+        <v>0</v>
+      </c>
+      <c r="R183" s="12">
+        <v>0</v>
+      </c>
+      <c r="S183" s="12">
+        <v>0</v>
+      </c>
+      <c r="T183" s="12">
+        <v>0</v>
+      </c>
+      <c r="U183" s="12">
+        <v>0</v>
+      </c>
+      <c r="V183" s="12">
+        <v>0</v>
+      </c>
+      <c r="W183" s="12">
+        <v>0</v>
+      </c>
+      <c r="X183" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y183" s="12" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="184" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C184" s="12">
+        <v>300412</v>
+      </c>
+      <c r="D184" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E184" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="F184" s="22" t="s">
+        <v>331</v>
+      </c>
+      <c r="G184" s="14">
+        <v>0</v>
+      </c>
+      <c r="H184" s="12">
+        <v>0</v>
+      </c>
+      <c r="I184" s="12">
+        <v>0</v>
+      </c>
+      <c r="J184" s="12">
+        <v>0</v>
+      </c>
+      <c r="K184" s="12">
+        <v>0</v>
+      </c>
+      <c r="L184" s="12">
+        <v>0</v>
+      </c>
+      <c r="M184" s="14">
+        <v>0</v>
+      </c>
+      <c r="N184" s="14">
+        <v>0</v>
+      </c>
+      <c r="O184" s="14">
+        <v>0</v>
+      </c>
+      <c r="P184" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q184" s="12">
+        <v>0</v>
+      </c>
+      <c r="R184" s="12">
+        <v>0</v>
+      </c>
+      <c r="S184" s="12">
+        <v>0</v>
+      </c>
+      <c r="T184" s="12">
+        <v>0</v>
+      </c>
+      <c r="U184" s="12">
+        <v>0</v>
+      </c>
+      <c r="V184" s="12">
+        <v>0</v>
+      </c>
+      <c r="W184" s="12">
+        <v>0</v>
+      </c>
+      <c r="X184" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y184" s="12" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="185" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C185" s="12">
+        <v>300413</v>
+      </c>
+      <c r="D185" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E185" s="13" t="s">
+        <v>352</v>
+      </c>
+      <c r="F185" s="22" t="s">
+        <v>324</v>
+      </c>
+      <c r="G185" s="14">
+        <v>0</v>
+      </c>
+      <c r="H185" s="12">
+        <v>0</v>
+      </c>
+      <c r="I185" s="12">
+        <v>0</v>
+      </c>
+      <c r="J185" s="12">
+        <v>0</v>
+      </c>
+      <c r="K185" s="12">
+        <v>0</v>
+      </c>
+      <c r="L185" s="12">
+        <v>0</v>
+      </c>
+      <c r="M185" s="14">
+        <v>0</v>
+      </c>
+      <c r="N185" s="14">
+        <v>0</v>
+      </c>
+      <c r="O185" s="14">
+        <v>0</v>
+      </c>
+      <c r="P185" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q185" s="12">
+        <v>0</v>
+      </c>
+      <c r="R185" s="12">
+        <v>0.03</v>
+      </c>
+      <c r="S185" s="12">
+        <v>0</v>
+      </c>
+      <c r="T185" s="12">
+        <v>0</v>
+      </c>
+      <c r="U185" s="12">
+        <v>0</v>
+      </c>
+      <c r="V185" s="12">
+        <v>0</v>
+      </c>
+      <c r="W185" s="12">
+        <v>0</v>
+      </c>
+      <c r="X185" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y185" s="12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C186" s="12">
+        <v>300421</v>
+      </c>
+      <c r="D186" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E186" s="13" t="s">
+        <v>310</v>
+      </c>
+      <c r="F186" s="22" t="s">
+        <v>325</v>
+      </c>
+      <c r="G186" s="14">
+        <v>0</v>
+      </c>
+      <c r="H186" s="12">
+        <v>0</v>
+      </c>
+      <c r="I186" s="12">
+        <v>0</v>
+      </c>
+      <c r="J186" s="12">
+        <v>0</v>
+      </c>
+      <c r="K186" s="12">
+        <v>0</v>
+      </c>
+      <c r="L186" s="12">
+        <v>0</v>
+      </c>
+      <c r="M186" s="14">
+        <v>0</v>
+      </c>
+      <c r="N186" s="14">
+        <v>0</v>
+      </c>
+      <c r="O186" s="14">
+        <v>0</v>
+      </c>
+      <c r="P186" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q186" s="12">
+        <v>0</v>
+      </c>
+      <c r="R186" s="12">
+        <v>0</v>
+      </c>
+      <c r="S186" s="12">
+        <v>0</v>
+      </c>
+      <c r="T186" s="12">
+        <v>0</v>
+      </c>
+      <c r="U186" s="12">
+        <v>0</v>
+      </c>
+      <c r="V186" s="12">
+        <v>0</v>
+      </c>
+      <c r="W186" s="12">
+        <v>0</v>
+      </c>
+      <c r="X186" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y186" s="12" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="187" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C187" s="12">
+        <v>300422</v>
+      </c>
+      <c r="D187" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E187" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="F187" s="22" t="s">
+        <v>326</v>
+      </c>
+      <c r="G187" s="14">
+        <v>0</v>
+      </c>
+      <c r="H187" s="12">
+        <v>0</v>
+      </c>
+      <c r="I187" s="12">
+        <v>0</v>
+      </c>
+      <c r="J187" s="12">
+        <v>0</v>
+      </c>
+      <c r="K187" s="12">
+        <v>0</v>
+      </c>
+      <c r="L187" s="12">
+        <v>0</v>
+      </c>
+      <c r="M187" s="14">
+        <v>0</v>
+      </c>
+      <c r="N187" s="14">
+        <v>0</v>
+      </c>
+      <c r="O187" s="14">
+        <v>0</v>
+      </c>
+      <c r="P187" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q187" s="12">
+        <v>0</v>
+      </c>
+      <c r="R187" s="12">
+        <v>0</v>
+      </c>
+      <c r="S187" s="12">
+        <v>0</v>
+      </c>
+      <c r="T187" s="12">
+        <v>0</v>
+      </c>
+      <c r="U187" s="12">
+        <v>0</v>
+      </c>
+      <c r="V187" s="12">
+        <v>0</v>
+      </c>
+      <c r="W187" s="12">
+        <v>0</v>
+      </c>
+      <c r="X187" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y187" s="12" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="188" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C188" s="12">
+        <v>300423</v>
+      </c>
+      <c r="D188" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E188" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F188" s="22" t="s">
+        <v>327</v>
+      </c>
+      <c r="G188" s="14">
+        <v>0</v>
+      </c>
+      <c r="H188" s="12">
+        <v>0</v>
+      </c>
+      <c r="I188" s="12">
+        <v>0</v>
+      </c>
+      <c r="J188" s="12">
+        <v>0</v>
+      </c>
+      <c r="K188" s="12">
+        <v>0</v>
+      </c>
+      <c r="L188" s="12">
+        <v>0</v>
+      </c>
+      <c r="M188" s="14">
+        <v>0</v>
+      </c>
+      <c r="N188" s="14">
+        <v>0</v>
+      </c>
+      <c r="O188" s="14">
+        <v>0</v>
+      </c>
+      <c r="P188" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q188" s="12">
+        <v>0</v>
+      </c>
+      <c r="R188" s="12">
+        <v>0</v>
+      </c>
+      <c r="S188" s="12">
+        <v>0</v>
+      </c>
+      <c r="T188" s="12">
+        <v>0</v>
+      </c>
+      <c r="U188" s="12">
+        <v>0</v>
+      </c>
+      <c r="V188" s="12">
+        <v>0</v>
+      </c>
+      <c r="W188" s="12">
+        <v>0</v>
+      </c>
+      <c r="X188" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y188" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="189" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C189" s="12">
+        <v>300431</v>
+      </c>
+      <c r="D189" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E189" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="F189" s="22" t="s">
+        <v>328</v>
+      </c>
+      <c r="G189" s="14">
+        <v>0</v>
+      </c>
+      <c r="H189" s="12">
+        <v>0</v>
+      </c>
+      <c r="I189" s="12">
+        <v>0</v>
+      </c>
+      <c r="J189" s="12">
+        <v>0</v>
+      </c>
+      <c r="K189" s="12">
+        <v>0</v>
+      </c>
+      <c r="L189" s="12">
+        <v>0</v>
+      </c>
+      <c r="M189" s="14">
+        <v>0</v>
+      </c>
+      <c r="N189" s="14">
+        <v>0</v>
+      </c>
+      <c r="O189" s="14">
+        <v>0</v>
+      </c>
+      <c r="P189" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q189" s="12">
+        <v>0</v>
+      </c>
+      <c r="R189" s="12">
+        <v>0</v>
+      </c>
+      <c r="S189" s="12">
+        <v>0</v>
+      </c>
+      <c r="T189" s="12">
+        <v>0</v>
+      </c>
+      <c r="U189" s="12">
+        <v>0</v>
+      </c>
+      <c r="V189" s="12">
+        <v>0</v>
+      </c>
+      <c r="W189" s="12">
+        <v>0</v>
+      </c>
+      <c r="X189" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y189" s="12" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="190" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C190" s="12">
+        <v>300432</v>
+      </c>
+      <c r="D190" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E190" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="F190" s="22" t="s">
+        <v>329</v>
+      </c>
+      <c r="G190" s="14">
+        <v>0</v>
+      </c>
+      <c r="H190" s="12">
+        <v>0</v>
+      </c>
+      <c r="I190" s="12">
+        <v>0</v>
+      </c>
+      <c r="J190" s="12">
+        <v>0</v>
+      </c>
+      <c r="K190" s="12">
+        <v>0</v>
+      </c>
+      <c r="L190" s="12">
+        <v>0</v>
+      </c>
+      <c r="M190" s="14">
+        <v>0</v>
+      </c>
+      <c r="N190" s="14">
+        <v>0</v>
+      </c>
+      <c r="O190" s="14">
+        <v>0</v>
+      </c>
+      <c r="P190" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q190" s="12">
+        <v>0</v>
+      </c>
+      <c r="R190" s="12">
+        <v>0</v>
+      </c>
+      <c r="S190" s="12">
+        <v>0</v>
+      </c>
+      <c r="T190" s="12">
+        <v>0</v>
+      </c>
+      <c r="U190" s="12">
+        <v>0</v>
+      </c>
+      <c r="V190" s="12">
+        <v>0</v>
+      </c>
+      <c r="W190" s="12">
+        <v>0</v>
+      </c>
+      <c r="X190" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="12" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="191" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C191" s="12">
+        <v>300433</v>
+      </c>
+      <c r="D191" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E191" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="F191" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="G191" s="14">
+        <v>0</v>
+      </c>
+      <c r="H191" s="12">
+        <v>0</v>
+      </c>
+      <c r="I191" s="12">
+        <v>0</v>
+      </c>
+      <c r="J191" s="12">
+        <v>0</v>
+      </c>
+      <c r="K191" s="12">
+        <v>0</v>
+      </c>
+      <c r="L191" s="12">
+        <v>0</v>
+      </c>
+      <c r="M191" s="14">
+        <v>0</v>
+      </c>
+      <c r="N191" s="14">
+        <v>0</v>
+      </c>
+      <c r="O191" s="14">
+        <v>0</v>
+      </c>
+      <c r="P191" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q191" s="12">
+        <v>0</v>
+      </c>
+      <c r="R191" s="12">
+        <v>0</v>
+      </c>
+      <c r="S191" s="12">
+        <v>0</v>
+      </c>
+      <c r="T191" s="12">
+        <v>0</v>
+      </c>
+      <c r="U191" s="12">
+        <v>0</v>
+      </c>
+      <c r="V191" s="12">
+        <v>0</v>
+      </c>
+      <c r="W191" s="12">
+        <v>0</v>
+      </c>
+      <c r="X191" s="12">
+        <v>0</v>
+      </c>
+      <c r="Y191" s="12" t="s">
+        <v>321</v>
+      </c>
+    </row>
     <row r="192" spans="3:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="193" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
     <row r="194" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.15"/>
